--- a/Catalogo de Dados.xlsx
+++ b/Catalogo de Dados.xlsx
@@ -100,7 +100,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="433" uniqueCount="229">
   <si>
     <t>Nome</t>
   </si>
@@ -115,13 +115,685 @@
   </si>
   <si>
     <t>Linhagem dos dados</t>
+  </si>
+  <si>
+    <t>ID_SAEB</t>
+  </si>
+  <si>
+    <t>ID_REGIAO</t>
+  </si>
+  <si>
+    <t>ID_UF</t>
+  </si>
+  <si>
+    <t>ID_MUNICIPIO</t>
+  </si>
+  <si>
+    <t>ID_AREA</t>
+  </si>
+  <si>
+    <t>ID_ESCOLA</t>
+  </si>
+  <si>
+    <t>IN_PUBLICA</t>
+  </si>
+  <si>
+    <t>ID_LOCALIZACAO</t>
+  </si>
+  <si>
+    <t>PC_FORMACAO_DOCENTE_INICIAL</t>
+  </si>
+  <si>
+    <t>PC_FORMACAO_DOCENTE_FINAL</t>
+  </si>
+  <si>
+    <t>PC_FORMACAO_DOCENTE_MEDIO</t>
+  </si>
+  <si>
+    <t>NIVEL_SOCIO_ECONOMICO</t>
+  </si>
+  <si>
+    <t>NU_MATRICULADOS_CENSO_5EF</t>
+  </si>
+  <si>
+    <t>NU_PRESENTES_5EF</t>
+  </si>
+  <si>
+    <t>TAXA_PARTICIPACAO_5EF</t>
+  </si>
+  <si>
+    <t>Nivel_0_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_1_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_2_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_3_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_4_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_5_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_6_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_7_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_8_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_9_LP5</t>
+  </si>
+  <si>
+    <t>Nivel_0_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_1_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_2_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_3_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_4_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_5_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_6_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_7_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_8_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_9_MT5</t>
+  </si>
+  <si>
+    <t>Nivel_10_MT5</t>
+  </si>
+  <si>
+    <t>NU_MATRICULADOS_CENSO_9EF</t>
+  </si>
+  <si>
+    <t>NU_PRESENTES_9EF</t>
+  </si>
+  <si>
+    <t>TAXA_PARTICIPACAO_9EF</t>
+  </si>
+  <si>
+    <t>Nivel_0_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_1_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_2_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_3_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_4_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_5_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_6_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_7_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_8_LP9</t>
+  </si>
+  <si>
+    <t>Nivel_0_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_1_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_2_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_3_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_4_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_5_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_6_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_7_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_8_MT9</t>
+  </si>
+  <si>
+    <t>Nivel_9_MT9</t>
+  </si>
+  <si>
+    <t>NU_MATRICULADOS_CENSO_EM</t>
+  </si>
+  <si>
+    <t>NU_PRESENTES_EM</t>
+  </si>
+  <si>
+    <t>TAXA_PARTICIPACAO_EM</t>
+  </si>
+  <si>
+    <t>Nivel_0_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_1_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_2_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_3_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_4_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_5_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_6_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_7_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_8_LPEM</t>
+  </si>
+  <si>
+    <t>Nivel_0_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_1_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_2_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_3_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_4_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_5_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_6_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_7_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_8_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_9_MTEM</t>
+  </si>
+  <si>
+    <t>Nivel_10_MTEM</t>
+  </si>
+  <si>
+    <t>MEDIA_5EF_LP</t>
+  </si>
+  <si>
+    <t>MEDIA_5EF_MT</t>
+  </si>
+  <si>
+    <t>MEDIA_9EF_LP</t>
+  </si>
+  <si>
+    <t>MEDIA_9EF_MT</t>
+  </si>
+  <si>
+    <t>MEDIA_EM_LP</t>
+  </si>
+  <si>
+    <t>MEDIA_EM_MT</t>
+  </si>
+  <si>
+    <t>Ano de aplicação do Saeb</t>
+  </si>
+  <si>
+    <t>Código da Região</t>
+  </si>
+  <si>
+    <t>Código da Unidade da Federação</t>
+  </si>
+  <si>
+    <t>Máscaras dos Códigos de Municípios (são códigos fictícios)</t>
+  </si>
+  <si>
+    <t>Área</t>
+  </si>
+  <si>
+    <t>Máscaras dos Códigos de Escola (são códigos fictícios)</t>
+  </si>
+  <si>
+    <t>Indica se a escola é pública ou não</t>
+  </si>
+  <si>
+    <t>Indicador de Nível Socioeconômico (Inse)</t>
+  </si>
+  <si>
+    <t>Número de alunos matriculados no 5º ano no censo 2023</t>
+  </si>
+  <si>
+    <t>Número de alunos presentes na aplicação</t>
+  </si>
+  <si>
+    <t>Razão entre o total de alunos presentes no SAEB (NU_PRESENTES_5EF) e o total de alunos cadastrados no Censo Escolar que são público alvo do SAEB (NU_MATRICULADOS_CENSO_5EF)</t>
+  </si>
+  <si>
+    <t>Número de alunos matriculados no 9º ano no censo 2023</t>
+  </si>
+  <si>
+    <t>Razão entre o total de alunos presentes no SAEB (NU_PRESENTES_9EF) e o total de alunos cadastrados no Censo Escolar que são público alvo do SAEB (NU_MATRICULADOS_CENSO_9EF</t>
+  </si>
+  <si>
+    <t>Número de alunos matriculados na 3ª/4ª série do ensino médio tradicional ou integrado no censo 2023</t>
+  </si>
+  <si>
+    <t>Razão entre o total de alunos presentes no SAEB (NU_PRESENTES_EM) e o total de alunos cadastrados no Censo Escolar que são público alvo do SAEB (NU_MATRICULADOS_CENSO_EM)</t>
+  </si>
+  <si>
+    <t>Média em Língua Portuguesa 5º ano</t>
+  </si>
+  <si>
+    <t>Média em Matemática 5º ano</t>
+  </si>
+  <si>
+    <t>Média em Língua Portuguesa 9º ano</t>
+  </si>
+  <si>
+    <t>Média em Matemática 9º ano</t>
+  </si>
+  <si>
+    <t>Média em Língua Portuguesa 3ª/4ª série do ensino médio tradicional ou integrado</t>
+  </si>
+  <si>
+    <t>Média em Matemática 3ª/4ª série do ensino médio tradicional ou integrado</t>
+  </si>
+  <si>
+    <t>1 - Norte</t>
+  </si>
+  <si>
+    <t>2 - Nordeste</t>
+  </si>
+  <si>
+    <t>3 - Sudeste</t>
+  </si>
+  <si>
+    <t>4 - Sul</t>
+  </si>
+  <si>
+    <t>5 - Centro-Oeste</t>
+  </si>
+  <si>
+    <t>11-RO</t>
+  </si>
+  <si>
+    <t>12-AC</t>
+  </si>
+  <si>
+    <t>13-AM</t>
+  </si>
+  <si>
+    <t>14-RR</t>
+  </si>
+  <si>
+    <t>15-PA</t>
+  </si>
+  <si>
+    <t>16-AP</t>
+  </si>
+  <si>
+    <t>17-TO</t>
+  </si>
+  <si>
+    <t>21-MA</t>
+  </si>
+  <si>
+    <t>22-PI</t>
+  </si>
+  <si>
+    <t>23-CE</t>
+  </si>
+  <si>
+    <t>24-RN</t>
+  </si>
+  <si>
+    <t>25-PB</t>
+  </si>
+  <si>
+    <t>26-PE</t>
+  </si>
+  <si>
+    <t>27-AL</t>
+  </si>
+  <si>
+    <t>28-SE</t>
+  </si>
+  <si>
+    <t>29-BA</t>
+  </si>
+  <si>
+    <t>31-MG</t>
+  </si>
+  <si>
+    <t>32-ES</t>
+  </si>
+  <si>
+    <t>33-RJ</t>
+  </si>
+  <si>
+    <t>35-SP</t>
+  </si>
+  <si>
+    <t>41-PR</t>
+  </si>
+  <si>
+    <t>42-SC</t>
+  </si>
+  <si>
+    <t>43-RS</t>
+  </si>
+  <si>
+    <t>50-MS</t>
+  </si>
+  <si>
+    <t>51-MT</t>
+  </si>
+  <si>
+    <t>52-GO</t>
+  </si>
+  <si>
+    <t>53-DF</t>
+  </si>
+  <si>
+    <t>1 - Capital</t>
+  </si>
+  <si>
+    <t>2 - Interior</t>
+  </si>
+  <si>
+    <t>0 - Privada</t>
+  </si>
+  <si>
+    <t>1 - Pública</t>
+  </si>
+  <si>
+    <t>1 - Urbana</t>
+  </si>
+  <si>
+    <t>2 - Rural</t>
+  </si>
+  <si>
+    <t>Nível I</t>
+  </si>
+  <si>
+    <t>Nível II</t>
+  </si>
+  <si>
+    <t>Nível III</t>
+  </si>
+  <si>
+    <t>Nível IV</t>
+  </si>
+  <si>
+    <t>Nível V</t>
+  </si>
+  <si>
+    <t>Nível VI</t>
+  </si>
+  <si>
+    <t>Nível VII</t>
+  </si>
+  <si>
+    <t>Nível VIII</t>
+  </si>
+  <si>
+    <t>Num</t>
+  </si>
+  <si>
+    <t>Char</t>
+  </si>
+  <si>
+    <t>Localização da escola</t>
+  </si>
+  <si>
+    <t>0 a 100</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Indicador de Adequação da Formação Docente (Informação referente ao Grupo 1, para os Anos Iniciais do EF), variando de 0% a 100%</t>
+  </si>
+  <si>
+    <t>Indicador de Adequação da Formação Docente (Informação referente ao Grupo 1, para os Anos Finais do EF), variando de 0% a 100%</t>
+  </si>
+  <si>
+    <t>Indicador de Adequação da Formação Docente (Informação referente ao Grupo 1, para o Ensino Médio), variando de 0% a 100%</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da escola que apresentaram nível 0 na escala Saeb para língua portuguesa., tirando de (-00;125) na escala que varia de 0 a 500, calculada com base na Teoria de Resposta ao item (TRI). O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes  do 5º ano da da escola que apresentaram nível 1 na escala Saeb para língua portuguesa, tirando de (125;150).  O estudante consegue identificar informações explícitas muito óbvias na superfície de textos curtos</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 2 na escala Saeb para língua portuguesa, tirando de (150;175).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes  do 5º ano da da escola que apresentaram nível 3 na escala Saeb para língua portuguesa, tirando de (175;200).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 4 na escala Saeb para língua portuguesa, tirando de (200;225).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 5 na escala Saeb para língua portuguesa, tirando de (225;250).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 6 na escala Saeb para língua portuguesa, tirando de (250;275).   OO estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 7 na escala Saeb para língua portuguesa, tirando de (275;300).   O estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 8 na escala Saeb para língua portuguesa, tirando de (300;325).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 9 na escala Saeb para língua portuguesa, tirando de (325;00+).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 0 na escala Saeb para matemática, tirando de (-00;125) na escala que varia de 0 a 500, calculada com base na Teoria de Resposta ao item (TRI). O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 1 na escala Saeb para matemática, tirando de (125;150).  O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 2 na escala Saeb para matemática, tirando de (150;175).   O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 3 na escala Saeb para matemática, tirando de (175;200).   O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentual de estudantes do 5º ano da da escola que apresentaram nível 4 na escala Saeb para matemática, tirando de (200;225).    Os estudantes demonstram ter desenvolvido as competências mínimas e parciais esperadas para a sua etapa escolar, mas ainda não possuem total autonomia. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentual de estudantes do 5º ano da da escola que apresentaram nível 5 na escala Saeb para matemática, tirando de (225;250).   Os estudantes demonstram ter desenvolvido as competências mínimas e parciais esperadas para a sua etapa escolar, mas ainda não possuem total autonomia. </t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 6 na escala Saeb para matemática,, tirando de (250;275).   OO estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 7 na escala Saeb para matemática, tirando de (275;300).   O estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 8 na escala Saeb para matemática, tirando de (300;325).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 9 na escala Saeb para matemática,, tirando de (325;350).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 5º ano da da escola que apresentaram nível 10 na escala Saeb para matemática,, tirando de (350;00+).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 0 na escala Saeb para língua portuguesa., tirando de (-00;200) na escala que varia de 0 a 500, calculada com base na Teoria de Resposta ao item (TRI). O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes  do 9º ano da escola que apresentaram nível 1 na escala Saeb para língua portuguesa, tirando de (200;225).  O estudante consegue identificar informações explícitas muito óbvias na superfície de textos curtos</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 2 na escala Saeb para língua portuguesa, tirando de (225;250).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes  do 9º ano da escola que apresentaram nível 3 na escala Saeb para língua portuguesa, tirando de (250;275).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 4 na escala Saeb para língua portuguesa, tirando de (275;300).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 5 na escala Saeb para língua portuguesa, tirando de (300;325).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 6 na escala Saeb para língua portuguesa, tirando de (325;350).   OO estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 7 na escala Saeb para língua portuguesa, tirando de (350;375).   O estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 8 na escala Saeb para língua portuguesa, tirando de (375;00+).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 0 na escala Saeb para matemática, tirando de (-00;200) na escala que varia de 0 a 500, calculada com base na Teoria de Resposta ao item (TRI). O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 1 na escala Saeb para matemática, tirando de (200;225).  O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 2 na escala Saeb para matemática, tirando de (225;250).   O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 3 na escala Saeb para matemática, tirando de (250;275).   O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentual de estudantes do 9º ano da escola que apresentaram nível 4 na escala Saeb para matemática, tirando de (275;300).    Os estudantes demonstram ter desenvolvido as competências mínimas e parciais esperadas para a sua etapa escolar, mas ainda não possuem total autonomia. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentual de estudantes do 9º ano da escola que apresentaram nível 5 na escala Saeb para matemática, tirando de (300;325).   Os estudantes demonstram ter desenvolvido as competências mínimas e parciais esperadas para a sua etapa escolar, mas ainda não possuem total autonomia. </t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 6 na escala Saeb para matemática,, tirando de (325;350).   OO estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 7 na escala Saeb para matemática, tirando de (350;375).   O estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 8 na escala Saeb para matemática, tirando de (375;400).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9º ano da escola que apresentaram nível 9 na escala Saeb para matemática, tirando de (400;00+).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 3º e 4º ano do ensino médio da escola que apresentaram nível 0 na escala Saeb para língua portuguesa., tirando de (-00;225) na escala que varia de 0 a 500, calculada com base na Teoria de Resposta ao item (TRI). O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes  do 3º e 4º ano do ensino médio da escola que apresentaram nível 1 na escala Saeb para língua portuguesa, tirando de [225;250).  O estudante consegue identificar informações explícitas muito óbvias na superfície de textos curtos</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da escola que apresentaram nível 2 na escala Saeb para língua portuguesa, tirando de [250;275).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes  do  3º e 4º ano do ensino médio da escola que apresentaram nível 3 na escala Saeb para língua portuguesa, tirando de [275;300).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 3º e 4º ano do ensino médio da  escola que apresentaram nível 4 na escala Saeb para língua portuguesa, tirando de [300;325).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 5 na escala Saeb para língua portuguesa, tirando de [325;350).   O estudante começa a associar elementos e reconhecer assuntos globais em textos simples, mas ainda apresenta graves lacunas de conteúdo</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 6 na escala Saeb para língua portuguesa, tirando de [350;375).   OO estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 7 na escala Saeb para língua portuguesa, tirando de [375;400).   O estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 8 na escala Saeb para língua portuguesa, tirando de [400;00+).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 0 na escala Saeb para matemática, tirando de (-00;225) na escala que varia de 0 a 500, calculada com base na Teoria de Resposta ao item (TRI). O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 1 na escala Saeb para matemática, tirando de [225;250).  O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do 9 3º e 4º ano do ensino médio da  escola que apresentaram nível 2 na escala Saeb para matemática, tirando de [275;300).   O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 3 na escala Saeb para matemática, tirando de [275;300).   O estudante demonstra habilidades muito elementares ou não domina nenhuma das competências avaliadas para aquela etapa escolar.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 4 na escala Saeb para matemática, tirando de [300;325).    Os estudantes demonstram ter desenvolvido as competências mínimas e parciais esperadas para a sua etapa escolar, mas ainda não possuem total autonomia. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 5 na escala Saeb para matemática, tirando de [325;350).   Os estudantes demonstram ter desenvolvido as competências mínimas e parciais esperadas para a sua etapa escolar, mas ainda não possuem total autonomia. </t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 6 na escala Saeb para matemática,, tirando de [350;375).   OO estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 7 na escala Saeb para matemática, tirando de [375;400).   O estudante demonstra domínio pleno e sólido de todo o conteúdo curricular exigido para a sua série.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 8 na escala Saeb para matemática, tirando de [400;425).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 9 na escala Saeb para matemática, tirando de [425;450).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>Percentual de estudantes do  3º e 4º ano do ensino médio da  escola que apresentaram nível 10 na escala Saeb para matemática, tirando de (450;00+).   Os estudantes demonstram alto grau de autonomia intelectual, excelente raciocínio lógico e domínio completo de conteúdos complexos e abstratos.</t>
+  </si>
+  <si>
+    <t>0 a 500</t>
+  </si>
+  <si>
+    <t>Microdados Saeb 2023</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -150,6 +822,24 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -159,9 +849,70 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="6">
     <border>
       <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right/>
       <top/>
       <bottom/>
@@ -171,9 +922,69 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -478,11 +1289,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E1"/>
+  <dimension ref="A1:E128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="58.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="64.85546875" customWidth="1"/>
@@ -505,8 +1316,1781 @@
         <v>4</v>
       </c>
     </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="8">
+        <v>2023</v>
+      </c>
+      <c r="E2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>93</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="4"/>
+      <c r="B4" s="10"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="21"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="4"/>
+      <c r="B5" s="10"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="21"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="4"/>
+      <c r="B6" s="10"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="E6" s="21"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="21"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="4"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="4"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="10"/>
+      <c r="D10" s="15" t="s">
+        <v>120</v>
+      </c>
+      <c r="E10" s="21"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="4"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="E11" s="21"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="4"/>
+      <c r="B12" s="10"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="21"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="4"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="21"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="4"/>
+      <c r="B14" s="10"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E14" s="21"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="4"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E15" s="21"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="4"/>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="21"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="4"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="E17" s="21"/>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" s="4"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="E18" s="21"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="4"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="E19" s="21"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" s="4"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="15" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="21"/>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="4"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="E21" s="21"/>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" s="4"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="E22" s="21"/>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" s="4"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="E23" s="21"/>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" s="4"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="21"/>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="E25" s="21"/>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" s="4"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="15" t="s">
+        <v>136</v>
+      </c>
+      <c r="E26" s="21"/>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" s="4"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="21"/>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" s="4"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="E28" s="21"/>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" s="4"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="E29" s="21"/>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" s="4"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" s="21"/>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" s="4"/>
+      <c r="B31" s="10"/>
+      <c r="C31" s="10"/>
+      <c r="D31" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="E31" s="21"/>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" s="4"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="E32" s="21"/>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" s="4"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="E33" s="21"/>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" s="5"/>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="E34" s="21"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C35" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E35" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="E36" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" s="5"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="12" t="s">
+        <v>146</v>
+      </c>
+      <c r="E37" s="21"/>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="E38" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="8" t="s">
+        <v>148</v>
+      </c>
+      <c r="E40" s="21"/>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="D41" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="19"/>
+      <c r="D42" s="8" t="s">
+        <v>150</v>
+      </c>
+      <c r="E42" s="21"/>
+    </row>
+    <row r="43" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B43" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="C43" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D43" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E43" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>165</v>
+      </c>
+      <c r="C44" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A45" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="8" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>159</v>
+      </c>
+      <c r="D45" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E45" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C46" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="D46" s="8" t="s">
+        <v>151</v>
+      </c>
+      <c r="E46" s="21" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" s="4"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" s="21"/>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" s="4"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="8" t="s">
+        <v>153</v>
+      </c>
+      <c r="E48" s="21"/>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" s="4"/>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E49" s="21"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" s="4"/>
+      <c r="B50" s="14"/>
+      <c r="C50" s="14"/>
+      <c r="D50" s="8" t="s">
+        <v>155</v>
+      </c>
+      <c r="E50" s="21"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" s="4"/>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="8" t="s">
+        <v>156</v>
+      </c>
+      <c r="E51" s="21"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A52" s="4"/>
+      <c r="B52" s="14"/>
+      <c r="C52" s="14"/>
+      <c r="D52" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="E52" s="21"/>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" s="5"/>
+      <c r="B53" s="14"/>
+      <c r="C53" s="14"/>
+      <c r="D53" s="8" t="s">
+        <v>158</v>
+      </c>
+      <c r="E53" s="21"/>
+    </row>
+    <row r="54" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B54" s="8" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E54" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B55" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D55" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="E55" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B56" s="8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C56" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="16"/>
+      <c r="E56" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="8" t="s">
+        <v>167</v>
+      </c>
+      <c r="C57" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D57" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B58" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D58" s="8"/>
+      <c r="E58" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="C59" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D59" s="8"/>
+      <c r="E59" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B60" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C60" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D60" s="8"/>
+      <c r="E60" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B61" s="8" t="s">
+        <v>171</v>
+      </c>
+      <c r="C61" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D61" s="8"/>
+      <c r="E61" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B62" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="C62" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D62" s="8"/>
+      <c r="E62" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B63" s="8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C63" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D63" s="8"/>
+      <c r="E63" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B64" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="C64" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D64" s="8"/>
+      <c r="E64" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B65" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="C65" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D65" s="8"/>
+      <c r="E65" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B66" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="C66" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D66" s="8"/>
+      <c r="E66" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B67" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="C67" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D67" s="8"/>
+      <c r="E67" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>178</v>
+      </c>
+      <c r="C68" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D68" s="8"/>
+      <c r="E68" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B69" s="8" t="s">
+        <v>179</v>
+      </c>
+      <c r="C69" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D69" s="8"/>
+      <c r="E69" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>180</v>
+      </c>
+      <c r="C70" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D70" s="8"/>
+      <c r="E70" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B71" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="C71" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D71" s="8"/>
+      <c r="E71" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="8" t="s">
+        <v>182</v>
+      </c>
+      <c r="C72" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D72" s="8"/>
+      <c r="E72" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B73" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="C73" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D73" s="8"/>
+      <c r="E73" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="8" t="s">
+        <v>184</v>
+      </c>
+      <c r="C74" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D74" s="8"/>
+      <c r="E74" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B75" s="8" t="s">
+        <v>185</v>
+      </c>
+      <c r="C75" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D75" s="8"/>
+      <c r="E75" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B76" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C76" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" s="8"/>
+      <c r="E76" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B77" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="C77" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" s="8"/>
+      <c r="E77" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B78" s="8" t="s">
+        <v>103</v>
+      </c>
+      <c r="C78" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D78" s="8"/>
+      <c r="E78" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" ht="38.25" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B79" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C79" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D79" s="8"/>
+      <c r="E79" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B80" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="C80" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D80" s="16"/>
+      <c r="E80" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B81" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="C81" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D81" s="8"/>
+      <c r="E81" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="C82" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D82" s="8"/>
+      <c r="E82" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B83" s="8" t="s">
+        <v>190</v>
+      </c>
+      <c r="C83" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D83" s="8"/>
+      <c r="E83" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B84" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="C84" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D84" s="8"/>
+      <c r="E84" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B85" s="8" t="s">
+        <v>192</v>
+      </c>
+      <c r="C85" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D85" s="8"/>
+      <c r="E85" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="C86" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D86" s="8"/>
+      <c r="E86" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B87" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C87" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D87" s="8"/>
+      <c r="E87" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B88" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="C88" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D88" s="8"/>
+      <c r="E88" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B89" s="8" t="s">
+        <v>196</v>
+      </c>
+      <c r="C89" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D89" s="8"/>
+      <c r="E89" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B90" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="C90" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D90" s="8"/>
+      <c r="E90" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B91" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="C91" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D91" s="8"/>
+      <c r="E91" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B92" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="C92" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D92" s="8"/>
+      <c r="E92" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B93" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="C93" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D93" s="8"/>
+      <c r="E93" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B94" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="C94" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D94" s="8"/>
+      <c r="E94" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B95" s="8" t="s">
+        <v>202</v>
+      </c>
+      <c r="C95" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D95" s="8"/>
+      <c r="E95" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B96" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="C96" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D96" s="8"/>
+      <c r="E96" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B97" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="C97" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D97" s="8"/>
+      <c r="E97" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B98" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="C98" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D98" s="8"/>
+      <c r="E98" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B99" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="C99" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D99" s="8"/>
+      <c r="E99" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B100" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C100" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D100" s="8"/>
+      <c r="E100" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B101" s="8" t="s">
+        <v>101</v>
+      </c>
+      <c r="C101" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D101" s="8"/>
+      <c r="E101" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B102" s="8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D102" s="8"/>
+      <c r="E102" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B103" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D103" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E103" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B104" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="C104" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D104" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E104" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B105" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="C105" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D105" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E105" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B106" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="C106" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D106" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E106" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B107" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="C107" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D107" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E107" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B108" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="C108" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D108" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E108" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B109" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="C109" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D109" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E109" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B110" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="C110" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D110" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E110" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B111" s="8" t="s">
+        <v>215</v>
+      </c>
+      <c r="C111" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D111" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E111" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5" ht="76.5" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B112" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="C112" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D112" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E112" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>217</v>
+      </c>
+      <c r="C113" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D113" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E113" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B114" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C114" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D114" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E114" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B115" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="C115" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D115" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E115" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B116" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="C116" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D116" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E116" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B117" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="C117" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D117" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E117" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B118" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="C118" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D118" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E118" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5" ht="51" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B119" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="C119" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D119" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E119" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B120" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="C120" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D120" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E120" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B121" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C121" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D121" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E121" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5" ht="63.75" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B122" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="C122" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D122" s="8" t="s">
+        <v>162</v>
+      </c>
+      <c r="E122" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B123" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C123" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D123" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E123" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B124" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C124" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D124" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E124" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B125" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="C125" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D125" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E125" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B126" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="C126" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D126" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E126" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B127" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C127" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D127" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E127" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="C128" s="17" t="s">
+        <v>159</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="E128" t="s">
+        <v>228</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:E1"/>
+  <mergeCells count="24">
+    <mergeCell ref="E8:E34"/>
+    <mergeCell ref="E3:E7"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="E39:E40"/>
+    <mergeCell ref="E41:E42"/>
+    <mergeCell ref="E46:E53"/>
+    <mergeCell ref="C3:C7"/>
+    <mergeCell ref="C8:C34"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="C46:C53"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B8:B34"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="B41:B42"/>
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="A8:A34"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A46:A53"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
